--- a/artfynd/A 40791-2025 artfynd.xlsx
+++ b/artfynd/A 40791-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89119525</v>
+        <v>89119526</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532568.8295253804</v>
+        <v>532611</v>
       </c>
       <c r="R2" t="n">
-        <v>6905341.162297589</v>
+        <v>6905349</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2020-08-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89119527</v>
+        <v>89119522</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532663.010952508</v>
+        <v>532538</v>
       </c>
       <c r="R3" t="n">
-        <v>6905341.145673351</v>
+        <v>6905355</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +840,9 @@
           <t>2020-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89119523</v>
+        <v>89119525</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532544.0532751132</v>
+        <v>532569</v>
       </c>
       <c r="R4" t="n">
-        <v>6905347.905621751</v>
+        <v>6905341</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,19 +937,9 @@
           <t>2020-08-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,12 +969,7 @@
         <v>89119524</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532571.1830950843</v>
+        <v>532571</v>
       </c>
       <c r="R5" t="n">
-        <v>6905338.857293943</v>
+        <v>6905339</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,19 +1034,9 @@
           <t>2020-08-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89119522</v>
+        <v>89119523</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532537.9250470443</v>
+        <v>532544</v>
       </c>
       <c r="R6" t="n">
-        <v>6905354.829702188</v>
+        <v>6905348</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1196,19 +1131,9 @@
           <t>2020-08-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89119526</v>
+        <v>89119527</v>
       </c>
       <c r="B7" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532611.1814025332</v>
+        <v>532663</v>
       </c>
       <c r="R7" t="n">
-        <v>6905349.022238841</v>
+        <v>6905341</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,19 +1228,9 @@
           <t>2020-08-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-08-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
